--- a/game_conf/xls/道具@item.xlsx
+++ b/game_conf/xls/道具@item.xlsx
@@ -389,7 +389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,7 +756,6 @@
           <t>Icon_02</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>1</v>
       </c>
@@ -770,9 +769,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -808,7 +804,6 @@
           <t>Icon_03</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>1</v>
       </c>
@@ -822,9 +817,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
@@ -860,7 +852,6 @@
           <t>Icon_03</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>1</v>
       </c>
@@ -874,9 +865,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -912,7 +900,6 @@
           <t>Icon_01</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>1</v>
       </c>
@@ -926,9 +913,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -964,7 +948,6 @@
           <t>Icon_01</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>1</v>
       </c>
@@ -978,9 +961,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1016,7 +996,6 @@
           <t>Icon_04</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>1</v>
       </c>
@@ -1030,9 +1009,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1068,7 +1044,6 @@
           <t>Icon_04</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>1</v>
       </c>
@@ -1082,9 +1057,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1120,7 +1092,6 @@
           <t>Icon_04</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>1</v>
       </c>
@@ -1134,9 +1105,6 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1172,7 +1140,6 @@
           <t>Icon_04</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>1</v>
       </c>
@@ -1186,20 +1153,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ace币</t>
+          <t>勋章</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1213,18 +1177,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>对局通用筹码</t>
+          <t>成就勋章</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Icon_04</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Icon_05</t>
+        </is>
+      </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
@@ -1238,20 +1201,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Win Ace币</t>
+          <t>荣誉</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1265,18 +1225,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>获胜对局专用筹码</t>
+          <t>荣誉积分</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Icon_04</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Icon_05</t>
+        </is>
+      </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
@@ -1290,20 +1249,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>勋章</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1317,7 +1273,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>成就勋章</t>
+          <t>声望积分</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1328,7 +1284,6 @@
           <t>Icon_05</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>1</v>
       </c>
@@ -1342,20 +1297,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>荣誉</t>
+          <t>竞技场币</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1369,18 +1321,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>荣誉积分</t>
+          <t>竞技场玩法货币</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Icon_05</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>1</v>
       </c>
@@ -1394,20 +1345,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>友情点</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1421,18 +1369,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>声望积分</t>
+          <t>好友互动货币</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Icon_05</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>1</v>
       </c>
@@ -1446,20 +1393,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>竞技场币</t>
+          <t>VIP经验</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1473,18 +1417,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>竞技场玩法货币</t>
+          <t>VIP等级经验</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Icon_05</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>1</v>
       </c>
@@ -1498,20 +1441,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>友情点</t>
+          <t>技能点</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1525,7 +1465,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>好友互动货币</t>
+          <t>技能升级点数</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1536,7 +1476,6 @@
           <t>Icon_05</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>1</v>
       </c>
@@ -1550,20 +1489,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VIP经验</t>
+          <t>灵魂精华</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1577,7 +1513,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VIP等级经验</t>
+          <t>养成材料货币</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1585,10 +1521,9 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Icon_05</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Icon_06</t>
+        </is>
+      </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
@@ -1602,20 +1537,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>技能点</t>
+          <t>星尘</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1629,18 +1561,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>技能升级点数</t>
+          <t>高级养成货币</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Icon_05</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Icon_06</t>
+        </is>
+      </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
@@ -1654,20 +1585,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>灵魂精华</t>
+          <t>魅力值</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1681,18 +1609,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>养成材料货币</t>
+          <t>社交魅力值</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Icon_06</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>1</v>
       </c>
@@ -1706,20 +1633,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>星尘</t>
+          <t>对局积分</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1733,18 +1657,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>高级养成货币</t>
+          <t>对局结算积分</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Icon_06</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>1</v>
       </c>
@@ -1758,45 +1681,41 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114</v>
+        <v>10001</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>魅力值</t>
+          <t>改名卡</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E25" t="n">
-        <v>10101</v>
+        <v>20101</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>社交魅力值</t>
+          <t>修改游戏昵称的必需物品</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Icon_06</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Icon_name</t>
+        </is>
+      </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
@@ -1810,45 +1729,44 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115</v>
+        <v>10002</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>对局积分</t>
+          <t>经验药水</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="E26" t="n">
-        <v>10101</v>
+        <v>20201</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>对局结算积分</t>
+          <t>使用获得经验</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Icon_06</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Icon_01</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
@@ -1862,45 +1780,44 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>改名卡</t>
+          <t>体力药水(小)</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E27" t="n">
-        <v>20101</v>
+        <v>20202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>修改游戏昵称的必需物品</t>
+          <t>使用恢复50体力</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Icon_name</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Icon_01</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
@@ -1914,20 +1831,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>经验药水</t>
+          <t>体力药水(大)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1937,15 +1851,15 @@
         <v>202</v>
       </c>
       <c r="E28" t="n">
-        <v>20201</v>
+        <v>20202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>使用获得经验</t>
+          <t>使用恢复200体力</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1968,42 +1882,39 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10003</v>
+        <v>10005</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>体力药水(小)</t>
+          <t>钻石礼盒</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>202</v>
+        <v>901</v>
       </c>
       <c r="E29" t="n">
-        <v>20202</v>
+        <v>90103</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>使用恢复50体力</t>
+          <t>打开获得钻石</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Icon_01</t>
+          <t>Icon_GiftBag_002</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2022,47 +1933,44 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10004</v>
+        <v>20001</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>体力药水(大)</t>
+          <t>金币兑换物1</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>301</v>
+      </c>
+      <c r="E30" t="n">
+        <v>30101</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>可分解获得金币</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Icon_01</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>2</v>
       </c>
-      <c r="D30" t="n">
-        <v>202</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20202</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>使用恢复200体力</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Icon_01</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
-      </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
@@ -2076,46 +1984,43 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10005</v>
+        <v>20002</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>钻石礼盒</t>
+          <t>金币兑换物2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>901</v>
+        <v>301</v>
       </c>
       <c r="E31" t="n">
-        <v>90103</v>
+        <v>30101</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>打开获得钻石</t>
+          <t>可分解获得金币</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_002</t>
+          <t>Icon_02</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -2130,20 +2035,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金币兑换物1</t>
+          <t>金币兑换物3</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2161,11 +2063,11 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Icon_01</t>
+          <t>Icon_03</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2184,20 +2086,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20002</v>
+        <v>20004</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>金币兑换物2</t>
+          <t>金币兑换物4</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2215,11 +2114,11 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Icon_02</t>
+          <t>Icon_04</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2238,34 +2137,31 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20003</v>
+        <v>20011</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金币兑换物3</t>
+          <t>通用英雄碎片</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E34" t="n">
-        <v>30101</v>
+        <v>30301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>可分解获得金币</t>
+          <t>英雄养成通用碎片</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2273,7 +2169,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Icon_03</t>
+          <t>Icon_05</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2292,47 +2188,44 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20004</v>
+        <v>30001</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金币兑换物4</t>
+          <t>英雄升星礼包</t>
         </is>
       </c>
       <c r="C35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>901</v>
+      </c>
+      <c r="E35" t="n">
+        <v>90101</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>打开获得英雄碎片</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Icon_GiftBag_005</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>3</v>
       </c>
-      <c r="D35" t="n">
-        <v>301</v>
-      </c>
-      <c r="E35" t="n">
-        <v>30101</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>可分解获得金币</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Icon_04</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
@@ -2346,47 +2239,44 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20011</v>
+        <v>30002</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>通用英雄碎片</t>
+          <t>英雄进阶礼包</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>901</v>
+      </c>
+      <c r="E36" t="n">
+        <v>90101</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>打开获得英雄碎片</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Icon_GiftBag_004</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>3</v>
       </c>
-      <c r="D36" t="n">
-        <v>303</v>
-      </c>
-      <c r="E36" t="n">
-        <v>30301</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>英雄养成通用碎片</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Icon_05</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
@@ -2400,20 +2290,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30001</v>
+        <v>30003</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>英雄升星礼包</t>
+          <t>装备精英礼包</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2423,19 +2310,19 @@
         <v>901</v>
       </c>
       <c r="E37" t="n">
-        <v>90101</v>
+        <v>90102</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>打开获得英雄碎片</t>
+          <t>打开获得装备材料</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_005</t>
+          <t>Icon_GiftBag_003</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2454,20 +2341,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>30002</v>
+        <v>30004</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>英雄进阶礼包</t>
+          <t>装备传说礼包</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2477,11 +2361,11 @@
         <v>901</v>
       </c>
       <c r="E38" t="n">
-        <v>90101</v>
+        <v>90102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>打开获得英雄碎片</t>
+          <t>打开获得稀有装备材料</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2489,7 +2373,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_004</t>
+          <t>Icon_GiftBag_002</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2508,20 +2392,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>30003</v>
+        <v>30005</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>装备精英礼包</t>
+          <t>材料礼包</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2531,19 +2412,19 @@
         <v>901</v>
       </c>
       <c r="E39" t="n">
-        <v>90102</v>
+        <v>90103</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>打开获得装备材料</t>
+          <t>打开获得养成材料</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_003</t>
+          <t>Icon_GiftBag_001</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2562,20 +2443,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>30004</v>
+        <v>30006</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>装备传说礼包</t>
+          <t>每日金币礼包</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2585,23 +2463,20 @@
         <v>901</v>
       </c>
       <c r="E40" t="n">
-        <v>90102</v>
+        <v>90103</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>打开获得稀有装备材料</t>
+          <t>每日免费领取金币</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_002</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>3</v>
+          <t>Icon_GiftBag_001</t>
+        </is>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -2616,20 +2491,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>30005</v>
+        <v>30011</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>材料礼包</t>
+          <t>新手豪华礼包</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2639,19 +2511,19 @@
         <v>901</v>
       </c>
       <c r="E41" t="n">
-        <v>90103</v>
+        <v>90104</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>打开获得养成材料</t>
+          <t>新玩家豪华奖励</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_001</t>
+          <t>Icon_GiftBag_005</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2670,45 +2542,41 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30006</v>
+        <v>70001</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>每日金币礼包</t>
+          <t>青铜头像框</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>901</v>
+        <v>701</v>
       </c>
       <c r="E42" t="n">
-        <v>90103</v>
+        <v>70102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>每日免费领取金币</t>
+          <t>头像装饰框</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_001</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>icon_Avatar_001</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
@@ -2722,46 +2590,40 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>30011</v>
+        <v>70002</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>新手豪华礼包</t>
+          <t>白银头像框</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>901</v>
+        <v>701</v>
       </c>
       <c r="E43" t="n">
-        <v>90104</v>
+        <v>70102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>新玩家豪华奖励</t>
+          <t>头像装饰框</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Icon_GiftBag_005</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>3</v>
+          <t>icon_Avatar_002</t>
+        </is>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -2776,20 +2638,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70001</v>
+        <v>70003</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>青铜头像框</t>
+          <t>黄金头像框</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2811,10 +2670,9 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>icon_Avatar_001</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>icon_Avatar_003</t>
+        </is>
+      </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
@@ -2828,20 +2686,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>70002</v>
+        <v>70004</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>白银头像框</t>
+          <t>铂金头像框</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2863,10 +2718,9 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>icon_Avatar_002</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>icon_Avatar_004</t>
+        </is>
+      </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
@@ -2880,20 +2734,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70003</v>
+        <v>70005</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>黄金头像框</t>
+          <t>钻石头像框</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2915,10 +2766,9 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>icon_Avatar_003</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>icon_Avatar_005</t>
+        </is>
+      </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
@@ -2932,20 +2782,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>70004</v>
+        <v>70006</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>铂金头像框</t>
+          <t>大师头像框</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2967,10 +2814,9 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>icon_Avatar_004</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>icon_Avatar_006</t>
+        </is>
+      </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
@@ -2984,20 +2830,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70005</v>
+        <v>70007</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>钻石头像框</t>
+          <t>宗师头像框</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3019,10 +2862,9 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>icon_Avatar_005</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>icon_Avatar_007</t>
+        </is>
+      </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
@@ -3036,20 +2878,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>70006</v>
+        <v>70008</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大师头像框</t>
+          <t>守望头像框</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3071,10 +2910,9 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>icon_Avatar_006</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>icon_Avatar_008</t>
+        </is>
+      </c>
       <c r="J49" t="n">
         <v>1</v>
       </c>
@@ -3088,20 +2926,17 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70007</v>
+        <v>70011</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宗师头像框</t>
+          <t>默认头像</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3111,11 +2946,11 @@
         <v>701</v>
       </c>
       <c r="E50" t="n">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>头像装饰框</t>
+          <t>默认头像</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3123,10 +2958,9 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>icon_Avatar_007</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>icon_Avatar_000</t>
+        </is>
+      </c>
       <c r="J50" t="n">
         <v>1</v>
       </c>
@@ -3140,114 +2974,7 @@
           <t>101&amp;10</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>70008</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>守望头像框</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>7</v>
-      </c>
-      <c r="D51" t="n">
-        <v>701</v>
-      </c>
-      <c r="E51" t="n">
-        <v>70102</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>头像装饰框</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>icon_Avatar_008</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>商城购买</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>101&amp;10</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>70011</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>默认头像</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>7</v>
-      </c>
-      <c r="D52" t="n">
-        <v>701</v>
-      </c>
-      <c r="E52" t="n">
-        <v>70101</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>默认头像</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>icon_Avatar_000</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>商城购买</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>101&amp;10</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
         <v>0</v>
       </c>
     </row>
